--- a/AAII_Financials/Quarterly/AMTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>AMTM</t>
   </si>
@@ -656,235 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46024</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45933</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44925</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3490000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3478000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3237000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3925000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3561000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3491000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3416000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2212000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2142000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2051000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1983000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2136800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1956500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1274000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3130000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3133000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2911000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3474000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3193000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3124000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3055000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1970000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1936000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1851000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1789000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1854300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1779600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1096000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E10" s="3">
         <v>345000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>326000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>451000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>368000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>367000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>361000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>242000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>206000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>194000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>282500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>176800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>178000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,8 +915,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,8 +966,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,47 +1019,50 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="3">
         <v>16000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>32000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>35000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>21000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1072,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1065,46 +1087,49 @@
         <v>94000</v>
       </c>
       <c r="F15" s="3">
+        <v>94000</v>
+      </c>
+      <c r="G15" s="3">
         <v>121000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>118000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>120000</v>
       </c>
       <c r="I15" s="3">
         <v>120000</v>
       </c>
       <c r="J15" s="3">
-        <v>57000</v>
+        <v>120000</v>
       </c>
       <c r="K15" s="3">
         <v>57000</v>
       </c>
       <c r="L15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="M15" s="3">
         <v>58000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>56000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>74200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>74500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,108 +1145,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3337000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3335000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3120000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3782000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3444000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3368000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3305000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2180000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2061000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1977000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1912000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2067200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1914300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1202000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E18" s="3">
         <v>143000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>117000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>143000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>117000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>123000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>111000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>81000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>74000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>69600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>72000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,258 +1272,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-24000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-18000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-21000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-19000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E21" s="3">
         <v>261000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>232000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>279000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>253000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>251000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>252000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>112000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>155000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>151000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>142000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>153900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>134000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>91000</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E22" s="3">
         <v>73000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>74000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>92000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>88000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>86000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>87000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>108000</v>
       </c>
       <c r="K22" s="3">
         <v>108000</v>
       </c>
       <c r="L22" s="3">
-        <v>111000</v>
+        <v>108000</v>
       </c>
       <c r="M22" s="3">
         <v>111000</v>
       </c>
       <c r="N22" s="3">
+        <v>111000</v>
+      </c>
+      <c r="O22" s="3">
         <v>111600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>90300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E23" s="3">
         <v>78000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-54000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-22000</v>
       </c>
       <c r="L23" s="3">
         <v>-22000</v>
       </c>
       <c r="M23" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="N23" s="3">
         <v>-25000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>72000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E24" s="3">
         <v>24000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-76000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>17000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,108 +1588,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E26" s="3">
         <v>54000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>44000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>37000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>55000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E27" s="3">
         <v>54000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>44000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>40000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-41000</v>
       </c>
       <c r="M27" s="3">
         <v>-41000</v>
       </c>
       <c r="N27" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O27" s="3">
         <v>-6200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>52000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,8 +1747,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1740,8 +1800,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1853,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,108 +1906,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E32" s="3">
         <v>24000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>18000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>21000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>19000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E33" s="3">
         <v>54000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>44000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>40000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-41000</v>
       </c>
       <c r="M33" s="3">
         <v>-41000</v>
       </c>
       <c r="N33" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O33" s="3">
         <v>-6200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>52000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,113 +2065,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E35" s="3">
         <v>54000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>44000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>40000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-41000</v>
       </c>
       <c r="M35" s="3">
         <v>-41000</v>
       </c>
       <c r="N35" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O35" s="3">
         <v>-6200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>52000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46024</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45933</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44925</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2199,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,47 +2220,48 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>459000</v>
+      </c>
+      <c r="E41" s="3">
         <v>428000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>437000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>738000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>546000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>522000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>452000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>271100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>197400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>211100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>305000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,8 +2271,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2197,11 +2286,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2209,23 +2298,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>8000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>41500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>56000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2235,47 +2324,50 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2553000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2496000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2526000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2479000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2475000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2509000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2405000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2401000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1410300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1526900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1542100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1440000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,8 +2377,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2335,8 +2430,11 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2346,24 +2444,24 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>50000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>95000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,47 +2483,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3189000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3097000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2960000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3113000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3427000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3266000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3140000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3084000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1841600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1880200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1932000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1931000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,47 +2536,50 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E47" s="3">
         <v>216000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>218000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>196000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>198000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>193000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>124000</v>
       </c>
       <c r="J47" s="3">
         <v>124000</v>
       </c>
       <c r="K47" s="3">
+        <v>124000</v>
+      </c>
+      <c r="L47" s="3">
         <v>119700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>117100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>107100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>104000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,47 +2589,50 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E48" s="3">
         <v>105000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>108000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>325000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>115000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>133000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>140000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>394000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>233800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>282900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>301000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,58 +2642,64 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7378000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7467000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7564000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7658000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7691000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8011000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8091000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8179000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3709500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3765900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3822500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3879000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2748,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,47 +2801,50 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E52" s="3">
         <v>285000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>278000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>78000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>239000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>263000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>286000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>37200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2854,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,47 +2907,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11199000</v>
+      </c>
+      <c r="E54" s="3">
         <v>11170000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11198000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11460000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11808000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12004000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11919000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11974000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6069200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6174300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6320400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6413000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +2960,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +2983,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,47 +3004,48 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E57" s="3">
         <v>832000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>871000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>892000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>821000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>876000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>726000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>764000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>536600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>496600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>550600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>560000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,97 +3055,103 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E58" s="3">
         <v>40000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>41000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>109000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>43000</v>
       </c>
       <c r="H58" s="3">
         <v>43000</v>
       </c>
       <c r="I58" s="3">
+        <v>43000</v>
+      </c>
+      <c r="J58" s="3">
         <v>44000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>103000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>87700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>95300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>98000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>669000</v>
+      </c>
+      <c r="E59" s="3">
         <v>601000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>650000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>612000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>616000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>519000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>510000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>360000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>99200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>115200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>336000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,47 +3161,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2091000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2088000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2354000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2172000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2097000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1971000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1965000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1371200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1309000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1365000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1376000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,47 +3214,50 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3771000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3887000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3894000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4058000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4441000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>4636000</v>
       </c>
       <c r="I61" s="3">
         <v>4636000</v>
       </c>
       <c r="J61" s="3">
+        <v>4636000</v>
+      </c>
+      <c r="K61" s="3">
         <v>4836000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4035000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4188600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4230500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4234000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3125,47 +3267,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E62" s="3">
         <v>230000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>297000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>168000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>357000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>360000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>402000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>251000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>239100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>244700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>228900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>246000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3320,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3373,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3426,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,47 +3479,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6410000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6467000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6536000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6840000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7219000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7425000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7356000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7422000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5768000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5852200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5963200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5997000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3532,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3555,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3606,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,8 +3659,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3545,8 +3712,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,47 +3765,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-297000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-363000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-417000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-461000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-501000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-511000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-515000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-527000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>-445000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3818,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +3871,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +3924,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,58 +3977,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4695000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4609000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4556000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4505000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4458000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4427000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4475000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4460000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>264100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>286400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>375000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>3259000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,113 +4083,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46024</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45933</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44925</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E81" s="3">
         <v>54000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>44000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>40000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-41000</v>
       </c>
       <c r="M81" s="3">
         <v>-41000</v>
       </c>
       <c r="N81" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O81" s="3">
         <v>-6200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>52000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,44 +4217,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="E83" s="3">
         <v>9000</v>
       </c>
       <c r="F83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G83" s="3">
         <v>6000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>5000</v>
       </c>
       <c r="H83" s="3">
         <v>5000</v>
       </c>
       <c r="I83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4268,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4321,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4374,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4427,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4480,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,58 +4533,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E89" s="3">
         <v>225000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-136000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>270000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>106000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>57000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>110000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-113000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>238000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-83000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>132200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>126700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,58 +4609,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4713,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,58 +4766,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>275000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>483000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-3000</v>
       </c>
       <c r="M94" s="3">
         <v>-3000</v>
       </c>
       <c r="N94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-5300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,8 +4842,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4660,8 +4893,11 @@
       <c r="R96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +4946,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +4999,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,94 +5052,100 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-559000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-203000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-193000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-161000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-14000</v>
       </c>
       <c r="M100" s="3">
         <v>-14000</v>
       </c>
       <c r="N100" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="O100" s="3">
         <v>-14800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>29000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>10000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-16000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4910,54 +5158,60 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E102" s="3">
         <v>181000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-190000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-301000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>192000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>70000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>181000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>74000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-94000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>110200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>94000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>
